--- a/artfynd/A 64945-2023 artfynd.xlsx
+++ b/artfynd/A 64945-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131772634</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131772626</v>
       </c>
       <c r="B3" t="n">
-        <v>92552</v>
+        <v>92555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131772636</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>131772621</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>131772620</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>131772623</v>
       </c>
       <c r="B7" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>131772629</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>131772624</v>
       </c>
       <c r="B9" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>131772617</v>
       </c>
       <c r="B10" t="n">
-        <v>91825</v>
+        <v>91828</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>131772625</v>
       </c>
       <c r="B11" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>131772635</v>
       </c>
       <c r="B12" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131772619</v>
+        <v>131772637</v>
       </c>
       <c r="B13" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>564418</v>
+        <v>564305</v>
       </c>
       <c r="R13" t="n">
-        <v>6913711</v>
+        <v>6913748</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska och äldre ringhack på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2042,10 +2042,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131772637</v>
+        <v>131772619</v>
       </c>
       <c r="B14" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2085,10 +2085,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>564305</v>
+        <v>564418</v>
       </c>
       <c r="R14" t="n">
-        <v>6913748</v>
+        <v>6913711</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>färska och äldre ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2165,7 @@
         <v>131772628</v>
       </c>
       <c r="B15" t="n">
-        <v>92054</v>
+        <v>92057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131772630</v>
       </c>
       <c r="B16" t="n">
-        <v>91829</v>
+        <v>91832</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131772618</v>
+        <v>131772627</v>
       </c>
       <c r="B17" t="n">
-        <v>57899</v>
+        <v>91832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,42 +2387,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564419</v>
+        <v>564425</v>
       </c>
       <c r="R17" t="n">
-        <v>6913733</v>
+        <v>6913623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,12 +2456,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,10 +2483,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131772627</v>
+        <v>131772618</v>
       </c>
       <c r="B18" t="n">
-        <v>91829</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,34 +2494,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564425</v>
+        <v>564419</v>
       </c>
       <c r="R18" t="n">
-        <v>6913623</v>
+        <v>6913733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2561,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2571,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2606,7 +2606,7 @@
         <v>131772622</v>
       </c>
       <c r="B19" t="n">
-        <v>91849</v>
+        <v>91852</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>131772631</v>
       </c>
       <c r="B20" t="n">
-        <v>92289</v>
+        <v>92292</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 64945-2023 artfynd.xlsx
+++ b/artfynd/A 64945-2023 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131772627</v>
+        <v>131772618</v>
       </c>
       <c r="B17" t="n">
-        <v>91832</v>
+        <v>57902</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,34 +2387,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564425</v>
+        <v>564419</v>
       </c>
       <c r="R17" t="n">
-        <v>6913623</v>
+        <v>6913733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2454,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,7 +2464,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,10 +2496,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131772618</v>
+        <v>131772627</v>
       </c>
       <c r="B18" t="n">
-        <v>57902</v>
+        <v>91832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,42 +2507,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564419</v>
+        <v>564425</v>
       </c>
       <c r="R18" t="n">
-        <v>6913733</v>
+        <v>6913623</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2571,12 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 64945-2023 artfynd.xlsx
+++ b/artfynd/A 64945-2023 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131772618</v>
+        <v>131772627</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>91832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,42 +2387,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564419</v>
+        <v>564425</v>
       </c>
       <c r="R17" t="n">
-        <v>6913733</v>
+        <v>6913623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,12 +2456,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,10 +2483,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131772627</v>
+        <v>131772618</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>57902</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,34 +2494,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564425</v>
+        <v>564419</v>
       </c>
       <c r="R18" t="n">
-        <v>6913623</v>
+        <v>6913733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2561,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2571,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 64945-2023 artfynd.xlsx
+++ b/artfynd/A 64945-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131772634</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>131772626</v>
       </c>
       <c r="B3" t="n">
-        <v>92555</v>
+        <v>92561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>131772636</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>131772621</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
         <v>131772620</v>
       </c>
       <c r="B6" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>131772623</v>
       </c>
       <c r="B7" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1368,7 +1368,7 @@
         <v>131772629</v>
       </c>
       <c r="B8" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>131772624</v>
       </c>
       <c r="B9" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>131772617</v>
       </c>
       <c r="B10" t="n">
-        <v>91828</v>
+        <v>91834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>131772625</v>
       </c>
       <c r="B11" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>131772635</v>
       </c>
       <c r="B12" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>131772637</v>
       </c>
       <c r="B13" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,7 +2045,7 @@
         <v>131772619</v>
       </c>
       <c r="B14" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>131772628</v>
       </c>
       <c r="B15" t="n">
-        <v>92057</v>
+        <v>92063</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131772630</v>
       </c>
       <c r="B16" t="n">
-        <v>91832</v>
+        <v>91838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131772618</v>
+        <v>131772627</v>
       </c>
       <c r="B17" t="n">
-        <v>57902</v>
+        <v>91838</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,42 +2387,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564419</v>
+        <v>564425</v>
       </c>
       <c r="R17" t="n">
-        <v>6913733</v>
+        <v>6913623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,12 +2456,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,10 +2483,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131772627</v>
+        <v>131772618</v>
       </c>
       <c r="B18" t="n">
-        <v>91832</v>
+        <v>57904</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,34 +2494,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564425</v>
+        <v>564419</v>
       </c>
       <c r="R18" t="n">
-        <v>6913623</v>
+        <v>6913733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2561,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2571,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2606,7 +2606,7 @@
         <v>131772622</v>
       </c>
       <c r="B19" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>131772631</v>
       </c>
       <c r="B20" t="n">
-        <v>92292</v>
+        <v>92298</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 64945-2023 artfynd.xlsx
+++ b/artfynd/A 64945-2023 artfynd.xlsx
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131772623</v>
+        <v>131772629</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,30 +1273,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564455</v>
+        <v>564379</v>
       </c>
       <c r="R7" t="n">
-        <v>6913681</v>
+        <v>6913668</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131772629</v>
+        <v>131772623</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>91858</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,42 +1393,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564379</v>
+        <v>564455</v>
       </c>
       <c r="R8" t="n">
-        <v>6913668</v>
+        <v>6913681</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,7 +1448,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,12 +1458,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ett färskt ringhack på tall</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 64945-2023 artfynd.xlsx
+++ b/artfynd/A 64945-2023 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>131772626</v>
       </c>
       <c r="B3" t="n">
-        <v>92612</v>
+        <v>92615</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131772623</v>
+        <v>131772629</v>
       </c>
       <c r="B7" t="n">
-        <v>91909</v>
+        <v>57948</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,30 +1273,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564455</v>
+        <v>564379</v>
       </c>
       <c r="R7" t="n">
-        <v>6913681</v>
+        <v>6913668</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1328,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1338,7 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131772629</v>
+        <v>131772623</v>
       </c>
       <c r="B8" t="n">
-        <v>57948</v>
+        <v>91912</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1376,42 +1393,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564379</v>
+        <v>564455</v>
       </c>
       <c r="R8" t="n">
-        <v>6913668</v>
+        <v>6913681</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1443,7 +1448,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,12 +1458,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>ett färskt ringhack på tall</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1608,7 +1608,7 @@
         <v>131772617</v>
       </c>
       <c r="B10" t="n">
-        <v>91885</v>
+        <v>91888</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>131772625</v>
       </c>
       <c r="B11" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>131772635</v>
       </c>
       <c r="B12" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2165,7 +2165,7 @@
         <v>131772628</v>
       </c>
       <c r="B15" t="n">
-        <v>92114</v>
+        <v>92117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>131772630</v>
       </c>
       <c r="B16" t="n">
-        <v>91889</v>
+        <v>91892</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131772618</v>
+        <v>131772627</v>
       </c>
       <c r="B17" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,42 +2387,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564419</v>
+        <v>564425</v>
       </c>
       <c r="R17" t="n">
-        <v>6913733</v>
+        <v>6913623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,12 +2456,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,10 +2483,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131772627</v>
+        <v>131772618</v>
       </c>
       <c r="B18" t="n">
-        <v>91889</v>
+        <v>57948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,34 +2494,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564425</v>
+        <v>564419</v>
       </c>
       <c r="R18" t="n">
-        <v>6913623</v>
+        <v>6913733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2561,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2571,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2606,7 +2606,7 @@
         <v>131772622</v>
       </c>
       <c r="B19" t="n">
-        <v>91909</v>
+        <v>91912</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>131772631</v>
       </c>
       <c r="B20" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 64945-2023 artfynd.xlsx
+++ b/artfynd/A 64945-2023 artfynd.xlsx
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131772627</v>
+        <v>131772618</v>
       </c>
       <c r="B17" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,34 +2387,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564425</v>
+        <v>564419</v>
       </c>
       <c r="R17" t="n">
-        <v>6913623</v>
+        <v>6913733</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2446,7 +2454,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2456,7 +2464,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2483,10 +2496,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131772618</v>
+        <v>131772627</v>
       </c>
       <c r="B18" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2494,42 +2507,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564419</v>
+        <v>564425</v>
       </c>
       <c r="R18" t="n">
-        <v>6913733</v>
+        <v>6913623</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2561,7 +2566,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2571,12 +2576,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 64945-2023 artfynd.xlsx
+++ b/artfynd/A 64945-2023 artfynd.xlsx
@@ -1262,10 +1262,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131772629</v>
+        <v>131772623</v>
       </c>
       <c r="B7" t="n">
-        <v>57948</v>
+        <v>91912</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,42 +1273,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>564379</v>
+        <v>564455</v>
       </c>
       <c r="R7" t="n">
-        <v>6913668</v>
+        <v>6913681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1328,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1338,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>ett färskt ringhack på tall</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131772623</v>
+        <v>131772629</v>
       </c>
       <c r="B8" t="n">
-        <v>91912</v>
+        <v>57948</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,30 +1376,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>564455</v>
+        <v>564379</v>
       </c>
       <c r="R8" t="n">
-        <v>6913681</v>
+        <v>6913668</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1448,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1458,7 +1453,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:16</t>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ett färskt ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2376,10 +2376,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131772618</v>
+        <v>131772627</v>
       </c>
       <c r="B17" t="n">
-        <v>57948</v>
+        <v>91892</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2387,42 +2387,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>564419</v>
+        <v>564425</v>
       </c>
       <c r="R17" t="n">
-        <v>6913733</v>
+        <v>6913623</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2454,7 +2446,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2464,12 +2456,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:27</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,10 +2483,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131772627</v>
+        <v>131772618</v>
       </c>
       <c r="B18" t="n">
-        <v>91892</v>
+        <v>57948</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,34 +2494,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Svartåstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>564425</v>
+        <v>564419</v>
       </c>
       <c r="R18" t="n">
-        <v>6913623</v>
+        <v>6913733</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2561,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2571,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
